--- a/R/scenarios_cont_stratified_fixed.xlsx
+++ b/R/scenarios_cont_stratified_fixed.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Research\01 Tom PC blocked randomisation\design effects\partclus_blockedrand\R\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Research\01 Tom PC blocked randomisation\design effects\clean files for public repo\R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10CB2FCA-502D-426E-B68A-A874B1EFDDE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A47C6FE-49A9-4728-84EC-0FD234C1FD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11620" yWindow="1740" windowWidth="23760" windowHeight="18060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scenarios" sheetId="1" r:id="rId1"/>
@@ -374,7 +374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
@@ -1514,7 +1514,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C50">
         <v>0.2</v>
@@ -1526,10 +1526,10 @@
         <v>0.25</v>
       </c>
       <c r="F50">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G50">
-        <v>96</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -1537,7 +1537,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C51">
         <v>0.8</v>
@@ -1549,10 +1549,10 @@
         <v>0.25</v>
       </c>
       <c r="F51">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>96</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -1560,7 +1560,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C52">
         <v>0.2</v>
@@ -1572,10 +1572,10 @@
         <v>0.25</v>
       </c>
       <c r="F52">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="G52">
-        <v>192</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -1583,7 +1583,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C53">
         <v>0.8</v>
@@ -1595,10 +1595,10 @@
         <v>0.25</v>
       </c>
       <c r="F53">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>192</v>
+        <v>288</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
@@ -1606,7 +1606,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C54">
         <v>0.2</v>
@@ -1618,10 +1618,10 @@
         <v>0.25</v>
       </c>
       <c r="F54">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G54">
-        <v>96</v>
+        <v>144</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -1629,7 +1629,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C55">
         <v>0.8</v>
@@ -1641,10 +1641,10 @@
         <v>0.25</v>
       </c>
       <c r="F55">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G55">
-        <v>96</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -1652,7 +1652,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C56">
         <v>0.2</v>
@@ -1664,10 +1664,10 @@
         <v>0.25</v>
       </c>
       <c r="F56">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="G56">
-        <v>192</v>
+        <v>288</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -1675,7 +1675,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C57">
         <v>0.8</v>
@@ -1687,10 +1687,10 @@
         <v>0.25</v>
       </c>
       <c r="F57">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="G57">
-        <v>192</v>
+        <v>288</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -1698,7 +1698,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C58">
         <v>0.2</v>
@@ -1721,7 +1721,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C59">
         <v>0.8</v>
@@ -1744,7 +1744,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C60">
         <v>0.2</v>
@@ -1767,7 +1767,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C61">
         <v>0.8</v>
@@ -1790,7 +1790,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C62">
         <v>0.2</v>
@@ -1813,7 +1813,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C63">
         <v>0.8</v>
@@ -1836,7 +1836,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C64">
         <v>0.2</v>
@@ -1859,7 +1859,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C65">
         <v>0.8</v>
@@ -1882,7 +1882,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C66">
         <v>0.2</v>
@@ -1905,7 +1905,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C67">
         <v>0.8</v>
@@ -1928,7 +1928,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C68">
         <v>0.2</v>
@@ -1951,7 +1951,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C69">
         <v>0.8</v>
@@ -1966,374 +1966,6 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70">
-        <v>8</v>
-      </c>
-      <c r="C70">
-        <v>0.2</v>
-      </c>
-      <c r="D70">
-        <v>0</v>
-      </c>
-      <c r="E70">
-        <v>0.25</v>
-      </c>
-      <c r="F70">
-        <v>0</v>
-      </c>
-      <c r="G70">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71">
-        <v>8</v>
-      </c>
-      <c r="C71">
-        <v>0.8</v>
-      </c>
-      <c r="D71">
-        <v>0</v>
-      </c>
-      <c r="E71">
-        <v>0.25</v>
-      </c>
-      <c r="F71">
-        <v>0</v>
-      </c>
-      <c r="G71">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72">
-        <v>8</v>
-      </c>
-      <c r="C72">
-        <v>0.2</v>
-      </c>
-      <c r="D72">
-        <v>0</v>
-      </c>
-      <c r="E72">
-        <v>0.25</v>
-      </c>
-      <c r="F72">
-        <v>0</v>
-      </c>
-      <c r="G72">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73">
-        <v>8</v>
-      </c>
-      <c r="C73">
-        <v>0.8</v>
-      </c>
-      <c r="D73">
-        <v>0</v>
-      </c>
-      <c r="E73">
-        <v>0.25</v>
-      </c>
-      <c r="F73">
-        <v>0</v>
-      </c>
-      <c r="G73">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74">
-        <v>10</v>
-      </c>
-      <c r="C74">
-        <v>0.2</v>
-      </c>
-      <c r="D74">
-        <v>0</v>
-      </c>
-      <c r="E74">
-        <v>0.25</v>
-      </c>
-      <c r="F74">
-        <v>0</v>
-      </c>
-      <c r="G74">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75">
-        <v>10</v>
-      </c>
-      <c r="C75">
-        <v>0.8</v>
-      </c>
-      <c r="D75">
-        <v>0</v>
-      </c>
-      <c r="E75">
-        <v>0.25</v>
-      </c>
-      <c r="F75">
-        <v>0</v>
-      </c>
-      <c r="G75">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76">
-        <v>10</v>
-      </c>
-      <c r="C76">
-        <v>0.2</v>
-      </c>
-      <c r="D76">
-        <v>0</v>
-      </c>
-      <c r="E76">
-        <v>0.25</v>
-      </c>
-      <c r="F76">
-        <v>0</v>
-      </c>
-      <c r="G76">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77">
-        <v>10</v>
-      </c>
-      <c r="C77">
-        <v>0.8</v>
-      </c>
-      <c r="D77">
-        <v>0</v>
-      </c>
-      <c r="E77">
-        <v>0.25</v>
-      </c>
-      <c r="F77">
-        <v>0</v>
-      </c>
-      <c r="G77">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A78">
-        <v>77</v>
-      </c>
-      <c r="B78">
-        <v>12</v>
-      </c>
-      <c r="C78">
-        <v>0.2</v>
-      </c>
-      <c r="D78">
-        <v>0</v>
-      </c>
-      <c r="E78">
-        <v>0.25</v>
-      </c>
-      <c r="F78">
-        <v>0</v>
-      </c>
-      <c r="G78">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79">
-        <v>12</v>
-      </c>
-      <c r="C79">
-        <v>0.8</v>
-      </c>
-      <c r="D79">
-        <v>0</v>
-      </c>
-      <c r="E79">
-        <v>0.25</v>
-      </c>
-      <c r="F79">
-        <v>0</v>
-      </c>
-      <c r="G79">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A80">
-        <v>79</v>
-      </c>
-      <c r="B80">
-        <v>12</v>
-      </c>
-      <c r="C80">
-        <v>0.2</v>
-      </c>
-      <c r="D80">
-        <v>0</v>
-      </c>
-      <c r="E80">
-        <v>0.25</v>
-      </c>
-      <c r="F80">
-        <v>0</v>
-      </c>
-      <c r="G80">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A81">
-        <v>80</v>
-      </c>
-      <c r="B81">
-        <v>12</v>
-      </c>
-      <c r="C81">
-        <v>0.8</v>
-      </c>
-      <c r="D81">
-        <v>0</v>
-      </c>
-      <c r="E81">
-        <v>0.25</v>
-      </c>
-      <c r="F81">
-        <v>0</v>
-      </c>
-      <c r="G81">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="B82">
-        <v>14</v>
-      </c>
-      <c r="C82">
-        <v>0.2</v>
-      </c>
-      <c r="D82">
-        <v>0</v>
-      </c>
-      <c r="E82">
-        <v>0.25</v>
-      </c>
-      <c r="F82">
-        <v>0</v>
-      </c>
-      <c r="G82">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="B83">
-        <v>14</v>
-      </c>
-      <c r="C83">
-        <v>0.8</v>
-      </c>
-      <c r="D83">
-        <v>0</v>
-      </c>
-      <c r="E83">
-        <v>0.25</v>
-      </c>
-      <c r="F83">
-        <v>0</v>
-      </c>
-      <c r="G83">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A84">
-        <v>83</v>
-      </c>
-      <c r="B84">
-        <v>14</v>
-      </c>
-      <c r="C84">
-        <v>0.2</v>
-      </c>
-      <c r="D84">
-        <v>0</v>
-      </c>
-      <c r="E84">
-        <v>0.25</v>
-      </c>
-      <c r="F84">
-        <v>0</v>
-      </c>
-      <c r="G84">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85">
-        <v>14</v>
-      </c>
-      <c r="C85">
-        <v>0.8</v>
-      </c>
-      <c r="D85">
-        <v>0</v>
-      </c>
-      <c r="E85">
-        <v>0.25</v>
-      </c>
-      <c r="F85">
-        <v>0</v>
-      </c>
-      <c r="G85">
         <v>288</v>
       </c>
     </row>
